--- a/data/trans_bre/IP21B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 46,83</t>
+          <t>-29,24; 45,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-42,21; 0,0</t>
+          <t>-44,3; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-63,99; 0,0</t>
+          <t>-57,99; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,47</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 20,33</t>
+          <t>-27,59; 17,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 37,68</t>
+          <t>-28,22; 37,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 42,96</t>
+          <t>-23,07; 43,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-79,95; 0,0</t>
+          <t>-80,82; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,31; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-47,39; 0,0</t>
+          <t>-49,31; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-45,44; -5,92</t>
+          <t>-46,15; -5,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,27; 58,98</t>
+          <t>-18,7; 58,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,94; 32,29</t>
+          <t>-31,08; 29,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 72,48</t>
+          <t>-15,13; 73,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 9,7</t>
+          <t>-14,51; 11,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 12,03</t>
+          <t>-16,32; 14,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 22,2</t>
+          <t>-20,79; 21,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 31,78</t>
+          <t>-30,15; 32,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-84,34; 201,84</t>
+          <t>-86,28; 214,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-74,76; 121,5</t>
+          <t>-73,48; 163,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 263,39</t>
+          <t>-63,61; 216,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-94,78; 337,47</t>
+          <t>-82,54; 492,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-29,24; 45,49</t>
+          <t>-27,89; 47,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-44,3; 0,0</t>
+          <t>-45,23; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-57,99; 0,0</t>
+          <t>-57,91; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 83,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 17,53</t>
+          <t>-30,65; 15,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 37,05</t>
+          <t>-30,66; 34,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 43,27</t>
+          <t>-23,3; 42,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-80,82; 0,0</t>
+          <t>-79,96; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,31; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-49,31; 0,0</t>
+          <t>-46,37; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-46,15; -5,92</t>
+          <t>-46,15; -5,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 58,91</t>
+          <t>-24,15; 59,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 29,63</t>
+          <t>-32,34; 33,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 73,73</t>
+          <t>-13,75; 72,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 11,02</t>
+          <t>-15,24; 10,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 14,84</t>
+          <t>-18,34; 13,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 21,02</t>
+          <t>-20,5; 20,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 32,53</t>
+          <t>-33,12; 29,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-86,28; 214,12</t>
+          <t>-84,24; 212,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-73,48; 163,44</t>
+          <t>-74,33; 143,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-63,61; 216,21</t>
+          <t>-63,23; 187,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-82,54; 492,8</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29,59</t>
+          <t>32,66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 47,14</t>
+          <t>-28,3; 46,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-45,23; 0,0</t>
+          <t>-42,21; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-57,91; 0,0</t>
+          <t>-63,99; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,47</t>
+          <t>0,0; 87,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-29,94</t>
+          <t>-30,12</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,65; 15,68</t>
+          <t>-24,18; 20,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,66; 34,7</t>
+          <t>-30,51; 37,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 42,86</t>
+          <t>-21,16; 42,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-79,96; 0,0</t>
+          <t>-82,64; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 0,0</t>
+          <t>-47,39; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-46,15; -5,8</t>
+          <t>-45,44; -5,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-38,81</t>
+          <t>-39,76</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 59,07</t>
+          <t>-19,27; 58,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 33,36</t>
+          <t>-29,94; 32,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 72,53</t>
+          <t>-13,74; 72,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,35</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-5,24%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 10,26</t>
+          <t>-15,7; 9,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 13,43</t>
+          <t>-16,98; 12,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 20,86</t>
+          <t>-20,88; 22,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 29,51</t>
+          <t>-32,09; 34,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-84,24; 212,71</t>
+          <t>-84,34; 201,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-74,33; 143,92</t>
+          <t>-74,76; 121,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-63,23; 187,57</t>
+          <t>-64,46; 263,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 367,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,44 +619,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-9,86</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-22,13</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>32,66</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>1.291627441686977</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-9.855129106733077</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-22.12949007944237</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>32.66161317142561</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.09467415116691327</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -655,254 +650,138 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-28,3; 46,83</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-42,21; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-63,99; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 87,94</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-28.29915330641891</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-42.211781465078</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-63.99028233947222</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>46.83035115676746</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>87.93865827305429</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-2,81</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6,05</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15,15</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-30,12</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-20,89%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>30,87%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>114,94%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-24,18; 20,33</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-30,51; 37,68</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-21,16; 42,96</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-82,64; 0,0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-2.806050821876177</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6.054699459043844</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>15.15098422821539</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-30.11562848037487</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2088694769627987</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.3086513982493808</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1.149402452678904</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-9,85</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-19,31</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-48,57</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-24.18210475097612</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-30.51304085561354</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-21.15845752070554</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-82.64072100797478</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-47,39; 0,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-45,44; -5,92</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>20.33451979430073</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>37.68120266175163</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>42.95505932087817</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +789,253 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6,85</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,53</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29,22</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-39,76</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>56,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-7,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>217,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n">
+        <v>-9.850259540110622</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-19.30955548638244</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-48.56774480105032</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-19,27; 58,98</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-29,94; 32,29</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-13,74; 72,48</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-47.3920599037379</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-45.44418729844557</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-5.918769769202879</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>6.847096861926214</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.532318684635167</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>29.21854267542585</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-39.75663572594764</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.560780842719409</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.07064927024038406</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>2.175964161842867</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-19.26684415206667</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-29.94072654065953</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-13.74165144889509</v>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>58.98340062999679</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>32.28804582752627</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>72.48242277504286</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-2,55</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,5</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-20,82%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-13,84%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-15,7; 9,7</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-16,98; 12,03</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-20,88; 22,2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-32,09; 34,39</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-84,34; 201,84</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-74,76; 121,5</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-64,46; 263,39</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 367,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-2.554704906982479</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.49521887869057</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.276135974439763</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.1949990453929296</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.208165500821786</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1384197247504137</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.06011278302960361</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.007363632267357125</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-15.69552620791438</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-16.97864242478489</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-20.88306294798407</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-32.08569542076016</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.8433909072628978</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.7475832540303866</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.644635578440933</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>9.702580252170407</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>12.02827703860551</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>22.19962105568049</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>34.38706574460353</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>2.018416933832388</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.214969012487765</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>2.633865428977699</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>3.67537607925836</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1043,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
